--- a/GIL.xlsx
+++ b/GIL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EC72C4-224A-49E2-9408-E8B37A9731E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1EA74A-259D-41DC-A880-DE99207370DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{8FF81416-71A4-47E4-A621-F1E8D8B5CE92}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{8FF81416-71A4-47E4-A621-F1E8D8B5CE92}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={425B13C0-9EEF-4FF4-B9DF-4B417E5D09AC}</author>
+    <author>tc={5E16E18E-42B1-4E89-9162-C7140307D0A5}</author>
+  </authors>
+  <commentList>
+    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{425B13C0-9EEF-4FF4-B9DF-4B417E5D09AC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Acquisition of HanesBrands</t>
+      </text>
+    </comment>
+    <comment ref="P16" authorId="1" shapeId="0" xr:uid="{5E16E18E-42B1-4E89-9162-C7140307D0A5}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Loss from discont. operations</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
   <si>
     <t>Gildan Activewear</t>
   </si>
@@ -197,6 +224,21 @@
   <si>
     <t>Q126</t>
   </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Acquisition of HanesBrand 01-12-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash and Stock deal for about $2,2 billion </t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
 </sst>
 </file>
 
@@ -205,13 +247,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -260,6 +308,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -280,23 +347,28 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -317,6 +389,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{8B33ADBE-04BB-4CBE-9B0B-CA0AD3C75760}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -634,9 +712,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="O8" dT="2026-08-18T08:55:26.00" personId="{8B33ADBE-04BB-4CBE-9B0B-CA0AD3C75760}" id="{425B13C0-9EEF-4FF4-B9DF-4B417E5D09AC}">
+    <text>Acquisition of HanesBrands</text>
+  </threadedComment>
+  <threadedComment ref="P16" dT="2026-08-18T09:02:47.13" personId="{8B33ADBE-04BB-4CBE-9B0B-CA0AD3C75760}" id="{5E16E18E-42B1-4E89-9162-C7140307D0A5}">
+    <text>Loss from discont. operations</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274EE32F-57FA-4DDA-8E39-E87CCA06F538}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="2" customWidth="1"/>
@@ -656,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>63.14</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -664,10 +753,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>186.15799999999999</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>52</v>
+        <v>185.17599999999999</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -679,7 +768,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>11754.016119999998</v>
+        <v>10349.486639999999</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -690,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>237.05500000000001</v>
+        <v>268.30200000000002</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>52</v>
@@ -701,8 +790,8 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <f>450+4265.1</f>
-        <v>4715.1000000000004</v>
+        <f>3585.88+945.181</f>
+        <v>4531.0609999999997</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>52</v>
@@ -714,7 +803,22 @@
       </c>
       <c r="I7" s="3">
         <f>+I4+I6-I5</f>
-        <v>16232.061119999998</v>
+        <v>14612.245639999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -726,8 +830,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0151822-DCFA-4201-859E-6001F7813102}">
-  <dimension ref="A1:BV185"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0151822-DCFA-4201-859E-6001F7813102}">
+  <dimension ref="A1:BY185"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -735,12 +839,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
@@ -780,29 +884,32 @@
       <c r="O2" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="T2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
@@ -827,9 +934,15 @@
       <c r="M3" s="2">
         <v>830.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:74" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
+      <c r="O3" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="B4" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="3"/>
@@ -858,8 +971,12 @@
         <v>80</v>
       </c>
       <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="O4" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>56</v>
+      </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
@@ -918,9 +1035,12 @@
       <c r="BT4" s="3"/>
       <c r="BU4" s="3"/>
       <c r="BV4" s="3"/>
-    </row>
-    <row r="5" spans="1:74" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
+      <c r="BW4" s="3"/>
+      <c r="BX4" s="3"/>
+      <c r="BY4" s="3"/>
+    </row>
+    <row r="5" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="B5" s="12" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="3"/>
@@ -952,7 +1072,9 @@
       <c r="O5" s="3">
         <v>1069.0999999999999</v>
       </c>
-      <c r="P5" s="3"/>
+      <c r="P5" s="3">
+        <v>1458.6</v>
+      </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -1011,8 +1133,11 @@
       <c r="BT5" s="3"/>
       <c r="BU5" s="3"/>
       <c r="BV5" s="3"/>
-    </row>
-    <row r="6" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW5" s="3"/>
+      <c r="BX5" s="3"/>
+      <c r="BY5" s="3"/>
+    </row>
+    <row r="6" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -1045,7 +1170,9 @@
       <c r="O6" s="3">
         <v>25</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="3">
+        <v>42.9</v>
+      </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -1104,8 +1231,11 @@
       <c r="BT6" s="3"/>
       <c r="BU6" s="3"/>
       <c r="BV6" s="3"/>
-    </row>
-    <row r="7" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW6" s="3"/>
+      <c r="BX6" s="3"/>
+      <c r="BY6" s="3"/>
+    </row>
+    <row r="7" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
@@ -1138,7 +1268,9 @@
       <c r="O7" s="3">
         <v>71.900000000000006</v>
       </c>
-      <c r="P7" s="3"/>
+      <c r="P7" s="3">
+        <v>101</v>
+      </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -1197,8 +1329,11 @@
       <c r="BT7" s="3"/>
       <c r="BU7" s="3"/>
       <c r="BV7" s="3"/>
-    </row>
-    <row r="8" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW7" s="3"/>
+      <c r="BX7" s="3"/>
+      <c r="BY7" s="3"/>
+    </row>
+    <row r="8" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>31</v>
       </c>
@@ -1237,9 +1372,11 @@
       <c r="O8" s="6">
         <v>1166</v>
       </c>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
+      <c r="P8" s="6">
+        <v>1582.4739999999999</v>
+      </c>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -1296,8 +1433,11 @@
       <c r="BT8" s="3"/>
       <c r="BU8" s="3"/>
       <c r="BV8" s="3"/>
-    </row>
-    <row r="9" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW8" s="3"/>
+      <c r="BX8" s="3"/>
+      <c r="BY8" s="3"/>
+    </row>
+    <row r="9" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
@@ -1330,7 +1470,9 @@
       <c r="O9" s="3">
         <v>887.59</v>
       </c>
-      <c r="P9" s="3"/>
+      <c r="P9" s="3">
+        <v>1122.712</v>
+      </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
@@ -1389,8 +1531,11 @@
       <c r="BT9" s="3"/>
       <c r="BU9" s="3"/>
       <c r="BV9" s="3"/>
-    </row>
-    <row r="10" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW9" s="3"/>
+      <c r="BX9" s="3"/>
+      <c r="BY9" s="3"/>
+    </row>
+    <row r="10" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
@@ -1423,7 +1568,7 @@
         <v>277.60699999999997</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" ref="J10:O10" si="1">+J8-J9</f>
+        <f t="shared" ref="J10:P10" si="1">+J8-J9</f>
         <v>821.5</v>
       </c>
       <c r="K10" s="3">
@@ -1446,7 +1591,10 @@
         <f t="shared" si="1"/>
         <v>278.40999999999997</v>
       </c>
-      <c r="P10" s="3"/>
+      <c r="P10" s="3">
+        <f t="shared" si="1"/>
+        <v>459.76199999999994</v>
+      </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
@@ -1505,8 +1653,11 @@
       <c r="BT10" s="3"/>
       <c r="BU10" s="3"/>
       <c r="BV10" s="3"/>
-    </row>
-    <row r="11" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW10" s="3"/>
+      <c r="BX10" s="3"/>
+      <c r="BY10" s="3"/>
+    </row>
+    <row r="11" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
@@ -1539,7 +1690,9 @@
       <c r="O11" s="3">
         <v>218.654</v>
       </c>
-      <c r="P11" s="3"/>
+      <c r="P11" s="3">
+        <v>193.84</v>
+      </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
@@ -1598,8 +1751,11 @@
       <c r="BT11" s="3"/>
       <c r="BU11" s="3"/>
       <c r="BV11" s="3"/>
-    </row>
-    <row r="12" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW11" s="3"/>
+      <c r="BX11" s="3"/>
+      <c r="BY11" s="3"/>
+    </row>
+    <row r="12" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>35</v>
       </c>
@@ -1632,7 +1788,9 @@
       <c r="O12" s="3">
         <v>60.976999999999997</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="P12" s="3">
+        <v>90.022999999999996</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
@@ -1691,8 +1849,11 @@
       <c r="BT12" s="3"/>
       <c r="BU12" s="3"/>
       <c r="BV12" s="3"/>
-    </row>
-    <row r="13" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW12" s="3"/>
+      <c r="BX12" s="3"/>
+      <c r="BY12" s="3"/>
+    </row>
+    <row r="13" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
@@ -1725,7 +1886,7 @@
         <v>192.94499999999996</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" ref="J13:O13" si="3">+J10-SUM(J11:J12)</f>
+        <f t="shared" ref="J13:P13" si="3">+J10-SUM(J11:J12)</f>
         <v>821.5</v>
       </c>
       <c r="K13" s="3">
@@ -1748,7 +1909,10 @@
         <f t="shared" si="3"/>
         <v>-1.2210000000000036</v>
       </c>
-      <c r="P13" s="3"/>
+      <c r="P13" s="3">
+        <f t="shared" si="3"/>
+        <v>175.89899999999994</v>
+      </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
@@ -1807,8 +1971,11 @@
       <c r="BT13" s="3"/>
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
-    </row>
-    <row r="14" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW13" s="3"/>
+      <c r="BX13" s="3"/>
+      <c r="BY13" s="3"/>
+    </row>
+    <row r="14" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
@@ -1841,7 +2008,9 @@
       <c r="O14" s="3">
         <v>66.733999999999995</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3">
+        <v>69.284999999999997</v>
+      </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
@@ -1900,8 +2069,11 @@
       <c r="BT14" s="3"/>
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
-    </row>
-    <row r="15" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW14" s="3"/>
+      <c r="BX14" s="3"/>
+      <c r="BY14" s="3"/>
+    </row>
+    <row r="15" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
@@ -1934,7 +2106,7 @@
         <v>162.72799999999995</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" ref="J15:O15" si="5">+J13-J14</f>
+        <f t="shared" ref="J15:P15" si="5">+J13-J14</f>
         <v>821.5</v>
       </c>
       <c r="K15" s="3">
@@ -1957,7 +2129,10 @@
         <f t="shared" si="5"/>
         <v>-67.954999999999998</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3">
+        <f t="shared" si="5"/>
+        <v>106.61399999999995</v>
+      </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
@@ -2016,8 +2191,11 @@
       <c r="BT15" s="3"/>
       <c r="BU15" s="3"/>
       <c r="BV15" s="3"/>
-    </row>
-    <row r="16" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW15" s="3"/>
+      <c r="BX15" s="3"/>
+      <c r="BY15" s="3"/>
+    </row>
+    <row r="16" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
@@ -2051,7 +2229,10 @@
         <f>-12.959+10.737</f>
         <v>-2.2219999999999995</v>
       </c>
-      <c r="P16" s="3"/>
+      <c r="P16" s="3">
+        <f>16.213+140.355</f>
+        <v>156.56799999999998</v>
+      </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
@@ -2110,8 +2291,11 @@
       <c r="BT16" s="3"/>
       <c r="BU16" s="3"/>
       <c r="BV16" s="3"/>
-    </row>
-    <row r="17" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW16" s="3"/>
+      <c r="BX16" s="3"/>
+      <c r="BY16" s="3"/>
+    </row>
+    <row r="17" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
@@ -2144,7 +2328,7 @@
         <v>131.47399999999996</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" ref="J17:O17" si="7">+J15-J16</f>
+        <f t="shared" ref="J17:P17" si="7">+J15-J16</f>
         <v>821.5</v>
       </c>
       <c r="K17" s="3">
@@ -2167,7 +2351,10 @@
         <f t="shared" si="7"/>
         <v>-65.733000000000004</v>
       </c>
-      <c r="P17" s="3"/>
+      <c r="P17" s="3">
+        <f t="shared" si="7"/>
+        <v>-49.954000000000036</v>
+      </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
@@ -2226,8 +2413,11 @@
       <c r="BT17" s="3"/>
       <c r="BU17" s="3"/>
       <c r="BV17" s="3"/>
-    </row>
-    <row r="18" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW17" s="3"/>
+      <c r="BX17" s="3"/>
+      <c r="BY17" s="3"/>
+    </row>
+    <row r="18" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -2300,13 +2490,16 @@
       <c r="BT18" s="3"/>
       <c r="BU18" s="3"/>
       <c r="BV18" s="3"/>
-    </row>
-    <row r="19" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW18" s="3"/>
+      <c r="BX18" s="3"/>
+      <c r="BY18" s="3"/>
+    </row>
+    <row r="19" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="7" t="e">
-        <f t="shared" ref="C19:O19" si="8">+C17/C20</f>
+        <f t="shared" ref="C19:P19" si="8">+C17/C20</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D19" s="7" t="e">
@@ -2357,9 +2550,12 @@
         <f t="shared" si="8"/>
         <v>-0.35310327786074197</v>
       </c>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
+      <c r="P19" s="7">
+        <f t="shared" si="8"/>
+        <v>-0.26976498034302521</v>
+      </c>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -2416,8 +2612,11 @@
       <c r="BT19" s="3"/>
       <c r="BU19" s="3"/>
       <c r="BV19" s="3"/>
-    </row>
-    <row r="20" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW19" s="3"/>
+      <c r="BX19" s="3"/>
+      <c r="BY19" s="3"/>
+    </row>
+    <row r="20" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>5</v>
       </c>
@@ -2450,7 +2649,9 @@
       <c r="O20" s="3">
         <v>186.15799999999999</v>
       </c>
-      <c r="P20" s="3"/>
+      <c r="P20" s="3">
+        <v>185.17599999999999</v>
+      </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
@@ -2509,8 +2710,11 @@
       <c r="BT20" s="3"/>
       <c r="BU20" s="3"/>
       <c r="BV20" s="3"/>
-    </row>
-    <row r="21" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW20" s="3"/>
+      <c r="BX20" s="3"/>
+      <c r="BY20" s="3"/>
+    </row>
+    <row r="21" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -2583,8 +2787,11 @@
       <c r="BT21" s="3"/>
       <c r="BU21" s="3"/>
       <c r="BV21" s="3"/>
-    </row>
-    <row r="22" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW21" s="3"/>
+      <c r="BX21" s="3"/>
+      <c r="BY21" s="3"/>
+    </row>
+    <row r="22" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B22" s="8" t="s">
         <v>46</v>
       </c>
@@ -2617,20 +2824,21 @@
         <v>0.11636116768499671</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22:O22" si="11">+M3/I3-1</f>
+        <f t="shared" ref="M22:P22" si="11">+M3/I3-1</f>
         <v>5.3659774197640564E-2</v>
       </c>
       <c r="N22" s="9" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O22" s="9">
-        <f t="shared" si="11"/>
-        <v>-1</v>
-      </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
+      <c r="O22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="P22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -2687,8 +2895,11 @@
       <c r="BT22" s="3"/>
       <c r="BU22" s="3"/>
       <c r="BV22" s="3"/>
-    </row>
-    <row r="23" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW22" s="3"/>
+      <c r="BX22" s="3"/>
+      <c r="BY22" s="3"/>
+    </row>
+    <row r="23" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
         <v>47</v>
       </c>
@@ -2721,20 +2932,21 @@
         <v>-0.23328025477707004</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" ref="M23:O23" si="13">+M4/I4-1</f>
+        <f t="shared" ref="M23:P23" si="13">+M4/I4-1</f>
         <v>-0.22178988326848248</v>
       </c>
       <c r="N23" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O23" s="9">
-        <f t="shared" si="13"/>
-        <v>-1</v>
-      </c>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
+      <c r="O23" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -2791,8 +3003,11 @@
       <c r="BT23" s="3"/>
       <c r="BU23" s="3"/>
       <c r="BV23" s="3"/>
-    </row>
-    <row r="24" spans="1:74" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="BW23" s="3"/>
+      <c r="BX23" s="3"/>
+      <c r="BY23" s="3"/>
+    </row>
+    <row r="24" spans="1:77" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="1" t="s">
         <v>48</v>
@@ -2826,7 +3041,7 @@
         <v>6.529807469264659E-2</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" ref="M24:O24" si="15">+M8/I8-1</f>
+        <f t="shared" ref="M24:N24" si="15">+M8/I8-1</f>
         <v>2.1876185324753772E-2</v>
       </c>
       <c r="N24" s="10">
@@ -2837,9 +3052,12 @@
         <f>+O8/K8-1</f>
         <v>0.63839521577355862</v>
       </c>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
+      <c r="P24" s="10">
+        <f>+P8/L8-1</f>
+        <v>0.72288949373979317</v>
+      </c>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
@@ -2896,8 +3114,11 @@
       <c r="BT24" s="6"/>
       <c r="BU24" s="6"/>
       <c r="BV24" s="6"/>
-    </row>
-    <row r="25" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW24" s="6"/>
+      <c r="BX24" s="6"/>
+      <c r="BY24" s="6"/>
+    </row>
+    <row r="25" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B25" s="8" t="s">
         <v>49</v>
       </c>
@@ -2950,12 +3171,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25" si="18">+O10/O8</f>
+        <f t="shared" ref="O25:P25" si="18">+O10/O8</f>
         <v>0.23877358490566036</v>
       </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
+      <c r="P25" s="9">
+        <f t="shared" si="18"/>
+        <v>0.29053368333381779</v>
+      </c>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -3012,8 +3236,11 @@
       <c r="BT25" s="3"/>
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
-    </row>
-    <row r="26" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW25" s="3"/>
+      <c r="BX25" s="3"/>
+      <c r="BY25" s="3"/>
+    </row>
+    <row r="26" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B26" s="8" t="s">
         <v>50</v>
       </c>
@@ -3066,12 +3293,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" ref="O26" si="21">+O13/O8</f>
+        <f t="shared" ref="O26:P26" si="21">+O13/O8</f>
         <v>-1.0471698113207579E-3</v>
       </c>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
+      <c r="P26" s="9">
+        <f t="shared" si="21"/>
+        <v>0.11115443286903921</v>
+      </c>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -3128,8 +3358,11 @@
       <c r="BT26" s="3"/>
       <c r="BU26" s="3"/>
       <c r="BV26" s="3"/>
-    </row>
-    <row r="27" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW26" s="3"/>
+      <c r="BX26" s="3"/>
+      <c r="BY26" s="3"/>
+    </row>
+    <row r="27" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B27" s="8" t="s">
         <v>51</v>
       </c>
@@ -3182,12 +3415,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" ref="O27" si="24">+O16/O15</f>
+        <f t="shared" ref="O27:P27" si="24">+O16/O15</f>
         <v>3.269810904274887E-2</v>
       </c>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
+      <c r="P27" s="9">
+        <f t="shared" si="24"/>
+        <v>1.4685500966102019</v>
+      </c>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -3244,8 +3480,11 @@
       <c r="BT27" s="3"/>
       <c r="BU27" s="3"/>
       <c r="BV27" s="3"/>
-    </row>
-    <row r="28" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW27" s="3"/>
+      <c r="BX27" s="3"/>
+      <c r="BY27" s="3"/>
+    </row>
+    <row r="28" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -3318,8 +3557,11 @@
       <c r="BT28" s="3"/>
       <c r="BU28" s="3"/>
       <c r="BV28" s="3"/>
-    </row>
-    <row r="29" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW28" s="3"/>
+      <c r="BX28" s="3"/>
+      <c r="BY28" s="3"/>
+    </row>
+    <row r="29" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -3392,8 +3634,11 @@
       <c r="BT29" s="3"/>
       <c r="BU29" s="3"/>
       <c r="BV29" s="3"/>
-    </row>
-    <row r="30" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW29" s="3"/>
+      <c r="BX29" s="3"/>
+      <c r="BY29" s="3"/>
+    </row>
+    <row r="30" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -3466,8 +3711,11 @@
       <c r="BT30" s="3"/>
       <c r="BU30" s="3"/>
       <c r="BV30" s="3"/>
-    </row>
-    <row r="31" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW30" s="3"/>
+      <c r="BX30" s="3"/>
+      <c r="BY30" s="3"/>
+    </row>
+    <row r="31" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -3540,8 +3788,11 @@
       <c r="BT31" s="3"/>
       <c r="BU31" s="3"/>
       <c r="BV31" s="3"/>
-    </row>
-    <row r="32" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW31" s="3"/>
+      <c r="BX31" s="3"/>
+      <c r="BY31" s="3"/>
+    </row>
+    <row r="32" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -3614,8 +3865,11 @@
       <c r="BT32" s="3"/>
       <c r="BU32" s="3"/>
       <c r="BV32" s="3"/>
-    </row>
-    <row r="33" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW32" s="3"/>
+      <c r="BX32" s="3"/>
+      <c r="BY32" s="3"/>
+    </row>
+    <row r="33" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -3688,8 +3942,11 @@
       <c r="BT33" s="3"/>
       <c r="BU33" s="3"/>
       <c r="BV33" s="3"/>
-    </row>
-    <row r="34" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW33" s="3"/>
+      <c r="BX33" s="3"/>
+      <c r="BY33" s="3"/>
+    </row>
+    <row r="34" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -3762,8 +4019,11 @@
       <c r="BT34" s="3"/>
       <c r="BU34" s="3"/>
       <c r="BV34" s="3"/>
-    </row>
-    <row r="35" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW34" s="3"/>
+      <c r="BX34" s="3"/>
+      <c r="BY34" s="3"/>
+    </row>
+    <row r="35" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -3836,8 +4096,11 @@
       <c r="BT35" s="3"/>
       <c r="BU35" s="3"/>
       <c r="BV35" s="3"/>
-    </row>
-    <row r="36" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW35" s="3"/>
+      <c r="BX35" s="3"/>
+      <c r="BY35" s="3"/>
+    </row>
+    <row r="36" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -3910,8 +4173,11 @@
       <c r="BT36" s="3"/>
       <c r="BU36" s="3"/>
       <c r="BV36" s="3"/>
-    </row>
-    <row r="37" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW36" s="3"/>
+      <c r="BX36" s="3"/>
+      <c r="BY36" s="3"/>
+    </row>
+    <row r="37" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -3984,8 +4250,11 @@
       <c r="BT37" s="3"/>
       <c r="BU37" s="3"/>
       <c r="BV37" s="3"/>
-    </row>
-    <row r="38" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW37" s="3"/>
+      <c r="BX37" s="3"/>
+      <c r="BY37" s="3"/>
+    </row>
+    <row r="38" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -4058,8 +4327,11 @@
       <c r="BT38" s="3"/>
       <c r="BU38" s="3"/>
       <c r="BV38" s="3"/>
-    </row>
-    <row r="39" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW38" s="3"/>
+      <c r="BX38" s="3"/>
+      <c r="BY38" s="3"/>
+    </row>
+    <row r="39" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4132,8 +4404,11 @@
       <c r="BT39" s="3"/>
       <c r="BU39" s="3"/>
       <c r="BV39" s="3"/>
-    </row>
-    <row r="40" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW39" s="3"/>
+      <c r="BX39" s="3"/>
+      <c r="BY39" s="3"/>
+    </row>
+    <row r="40" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -4206,8 +4481,11 @@
       <c r="BT40" s="3"/>
       <c r="BU40" s="3"/>
       <c r="BV40" s="3"/>
-    </row>
-    <row r="41" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW40" s="3"/>
+      <c r="BX40" s="3"/>
+      <c r="BY40" s="3"/>
+    </row>
+    <row r="41" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -4280,8 +4558,11 @@
       <c r="BT41" s="3"/>
       <c r="BU41" s="3"/>
       <c r="BV41" s="3"/>
-    </row>
-    <row r="42" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW41" s="3"/>
+      <c r="BX41" s="3"/>
+      <c r="BY41" s="3"/>
+    </row>
+    <row r="42" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -4354,8 +4635,11 @@
       <c r="BT42" s="3"/>
       <c r="BU42" s="3"/>
       <c r="BV42" s="3"/>
-    </row>
-    <row r="43" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW42" s="3"/>
+      <c r="BX42" s="3"/>
+      <c r="BY42" s="3"/>
+    </row>
+    <row r="43" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -4428,8 +4712,11 @@
       <c r="BT43" s="3"/>
       <c r="BU43" s="3"/>
       <c r="BV43" s="3"/>
-    </row>
-    <row r="44" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW43" s="3"/>
+      <c r="BX43" s="3"/>
+      <c r="BY43" s="3"/>
+    </row>
+    <row r="44" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -4502,8 +4789,11 @@
       <c r="BT44" s="3"/>
       <c r="BU44" s="3"/>
       <c r="BV44" s="3"/>
-    </row>
-    <row r="45" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW44" s="3"/>
+      <c r="BX44" s="3"/>
+      <c r="BY44" s="3"/>
+    </row>
+    <row r="45" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4576,8 +4866,11 @@
       <c r="BT45" s="3"/>
       <c r="BU45" s="3"/>
       <c r="BV45" s="3"/>
-    </row>
-    <row r="46" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW45" s="3"/>
+      <c r="BX45" s="3"/>
+      <c r="BY45" s="3"/>
+    </row>
+    <row r="46" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -4650,8 +4943,11 @@
       <c r="BT46" s="3"/>
       <c r="BU46" s="3"/>
       <c r="BV46" s="3"/>
-    </row>
-    <row r="47" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW46" s="3"/>
+      <c r="BX46" s="3"/>
+      <c r="BY46" s="3"/>
+    </row>
+    <row r="47" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -4724,8 +5020,11 @@
       <c r="BT47" s="3"/>
       <c r="BU47" s="3"/>
       <c r="BV47" s="3"/>
-    </row>
-    <row r="48" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW47" s="3"/>
+      <c r="BX47" s="3"/>
+      <c r="BY47" s="3"/>
+    </row>
+    <row r="48" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4798,8 +5097,11 @@
       <c r="BT48" s="3"/>
       <c r="BU48" s="3"/>
       <c r="BV48" s="3"/>
-    </row>
-    <row r="49" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW48" s="3"/>
+      <c r="BX48" s="3"/>
+      <c r="BY48" s="3"/>
+    </row>
+    <row r="49" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -4872,8 +5174,11 @@
       <c r="BT49" s="3"/>
       <c r="BU49" s="3"/>
       <c r="BV49" s="3"/>
-    </row>
-    <row r="50" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW49" s="3"/>
+      <c r="BX49" s="3"/>
+      <c r="BY49" s="3"/>
+    </row>
+    <row r="50" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -4946,8 +5251,11 @@
       <c r="BT50" s="3"/>
       <c r="BU50" s="3"/>
       <c r="BV50" s="3"/>
-    </row>
-    <row r="51" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW50" s="3"/>
+      <c r="BX50" s="3"/>
+      <c r="BY50" s="3"/>
+    </row>
+    <row r="51" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -5020,8 +5328,11 @@
       <c r="BT51" s="3"/>
       <c r="BU51" s="3"/>
       <c r="BV51" s="3"/>
-    </row>
-    <row r="52" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW51" s="3"/>
+      <c r="BX51" s="3"/>
+      <c r="BY51" s="3"/>
+    </row>
+    <row r="52" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -5094,8 +5405,11 @@
       <c r="BT52" s="3"/>
       <c r="BU52" s="3"/>
       <c r="BV52" s="3"/>
-    </row>
-    <row r="53" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW52" s="3"/>
+      <c r="BX52" s="3"/>
+      <c r="BY52" s="3"/>
+    </row>
+    <row r="53" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -5168,8 +5482,11 @@
       <c r="BT53" s="3"/>
       <c r="BU53" s="3"/>
       <c r="BV53" s="3"/>
-    </row>
-    <row r="54" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW53" s="3"/>
+      <c r="BX53" s="3"/>
+      <c r="BY53" s="3"/>
+    </row>
+    <row r="54" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -5242,8 +5559,11 @@
       <c r="BT54" s="3"/>
       <c r="BU54" s="3"/>
       <c r="BV54" s="3"/>
-    </row>
-    <row r="55" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW54" s="3"/>
+      <c r="BX54" s="3"/>
+      <c r="BY54" s="3"/>
+    </row>
+    <row r="55" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -5316,8 +5636,11 @@
       <c r="BT55" s="3"/>
       <c r="BU55" s="3"/>
       <c r="BV55" s="3"/>
-    </row>
-    <row r="56" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW55" s="3"/>
+      <c r="BX55" s="3"/>
+      <c r="BY55" s="3"/>
+    </row>
+    <row r="56" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -5390,8 +5713,11 @@
       <c r="BT56" s="3"/>
       <c r="BU56" s="3"/>
       <c r="BV56" s="3"/>
-    </row>
-    <row r="57" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW56" s="3"/>
+      <c r="BX56" s="3"/>
+      <c r="BY56" s="3"/>
+    </row>
+    <row r="57" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -5464,8 +5790,11 @@
       <c r="BT57" s="3"/>
       <c r="BU57" s="3"/>
       <c r="BV57" s="3"/>
-    </row>
-    <row r="58" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW57" s="3"/>
+      <c r="BX57" s="3"/>
+      <c r="BY57" s="3"/>
+    </row>
+    <row r="58" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -5538,8 +5867,11 @@
       <c r="BT58" s="3"/>
       <c r="BU58" s="3"/>
       <c r="BV58" s="3"/>
-    </row>
-    <row r="59" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW58" s="3"/>
+      <c r="BX58" s="3"/>
+      <c r="BY58" s="3"/>
+    </row>
+    <row r="59" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -5612,8 +5944,11 @@
       <c r="BT59" s="3"/>
       <c r="BU59" s="3"/>
       <c r="BV59" s="3"/>
-    </row>
-    <row r="60" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW59" s="3"/>
+      <c r="BX59" s="3"/>
+      <c r="BY59" s="3"/>
+    </row>
+    <row r="60" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -5686,8 +6021,11 @@
       <c r="BT60" s="3"/>
       <c r="BU60" s="3"/>
       <c r="BV60" s="3"/>
-    </row>
-    <row r="61" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW60" s="3"/>
+      <c r="BX60" s="3"/>
+      <c r="BY60" s="3"/>
+    </row>
+    <row r="61" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -5760,8 +6098,11 @@
       <c r="BT61" s="3"/>
       <c r="BU61" s="3"/>
       <c r="BV61" s="3"/>
-    </row>
-    <row r="62" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW61" s="3"/>
+      <c r="BX61" s="3"/>
+      <c r="BY61" s="3"/>
+    </row>
+    <row r="62" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -5834,8 +6175,11 @@
       <c r="BT62" s="3"/>
       <c r="BU62" s="3"/>
       <c r="BV62" s="3"/>
-    </row>
-    <row r="63" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW62" s="3"/>
+      <c r="BX62" s="3"/>
+      <c r="BY62" s="3"/>
+    </row>
+    <row r="63" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -5908,8 +6252,11 @@
       <c r="BT63" s="3"/>
       <c r="BU63" s="3"/>
       <c r="BV63" s="3"/>
-    </row>
-    <row r="64" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW63" s="3"/>
+      <c r="BX63" s="3"/>
+      <c r="BY63" s="3"/>
+    </row>
+    <row r="64" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -5982,8 +6329,11 @@
       <c r="BT64" s="3"/>
       <c r="BU64" s="3"/>
       <c r="BV64" s="3"/>
-    </row>
-    <row r="65" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW64" s="3"/>
+      <c r="BX64" s="3"/>
+      <c r="BY64" s="3"/>
+    </row>
+    <row r="65" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -6056,8 +6406,11 @@
       <c r="BT65" s="3"/>
       <c r="BU65" s="3"/>
       <c r="BV65" s="3"/>
-    </row>
-    <row r="66" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW65" s="3"/>
+      <c r="BX65" s="3"/>
+      <c r="BY65" s="3"/>
+    </row>
+    <row r="66" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -6130,8 +6483,11 @@
       <c r="BT66" s="3"/>
       <c r="BU66" s="3"/>
       <c r="BV66" s="3"/>
-    </row>
-    <row r="67" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW66" s="3"/>
+      <c r="BX66" s="3"/>
+      <c r="BY66" s="3"/>
+    </row>
+    <row r="67" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -6204,8 +6560,11 @@
       <c r="BT67" s="3"/>
       <c r="BU67" s="3"/>
       <c r="BV67" s="3"/>
-    </row>
-    <row r="68" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW67" s="3"/>
+      <c r="BX67" s="3"/>
+      <c r="BY67" s="3"/>
+    </row>
+    <row r="68" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -6278,8 +6637,11 @@
       <c r="BT68" s="3"/>
       <c r="BU68" s="3"/>
       <c r="BV68" s="3"/>
-    </row>
-    <row r="69" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW68" s="3"/>
+      <c r="BX68" s="3"/>
+      <c r="BY68" s="3"/>
+    </row>
+    <row r="69" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -6352,8 +6714,11 @@
       <c r="BT69" s="3"/>
       <c r="BU69" s="3"/>
       <c r="BV69" s="3"/>
-    </row>
-    <row r="70" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW69" s="3"/>
+      <c r="BX69" s="3"/>
+      <c r="BY69" s="3"/>
+    </row>
+    <row r="70" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -6426,8 +6791,11 @@
       <c r="BT70" s="3"/>
       <c r="BU70" s="3"/>
       <c r="BV70" s="3"/>
-    </row>
-    <row r="71" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW70" s="3"/>
+      <c r="BX70" s="3"/>
+      <c r="BY70" s="3"/>
+    </row>
+    <row r="71" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -6500,8 +6868,11 @@
       <c r="BT71" s="3"/>
       <c r="BU71" s="3"/>
       <c r="BV71" s="3"/>
-    </row>
-    <row r="72" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW71" s="3"/>
+      <c r="BX71" s="3"/>
+      <c r="BY71" s="3"/>
+    </row>
+    <row r="72" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -6574,8 +6945,11 @@
       <c r="BT72" s="3"/>
       <c r="BU72" s="3"/>
       <c r="BV72" s="3"/>
-    </row>
-    <row r="73" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW72" s="3"/>
+      <c r="BX72" s="3"/>
+      <c r="BY72" s="3"/>
+    </row>
+    <row r="73" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -6648,8 +7022,11 @@
       <c r="BT73" s="3"/>
       <c r="BU73" s="3"/>
       <c r="BV73" s="3"/>
-    </row>
-    <row r="74" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW73" s="3"/>
+      <c r="BX73" s="3"/>
+      <c r="BY73" s="3"/>
+    </row>
+    <row r="74" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -6722,8 +7099,11 @@
       <c r="BT74" s="3"/>
       <c r="BU74" s="3"/>
       <c r="BV74" s="3"/>
-    </row>
-    <row r="75" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW74" s="3"/>
+      <c r="BX74" s="3"/>
+      <c r="BY74" s="3"/>
+    </row>
+    <row r="75" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -6796,8 +7176,11 @@
       <c r="BT75" s="3"/>
       <c r="BU75" s="3"/>
       <c r="BV75" s="3"/>
-    </row>
-    <row r="76" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW75" s="3"/>
+      <c r="BX75" s="3"/>
+      <c r="BY75" s="3"/>
+    </row>
+    <row r="76" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -6870,8 +7253,11 @@
       <c r="BT76" s="3"/>
       <c r="BU76" s="3"/>
       <c r="BV76" s="3"/>
-    </row>
-    <row r="77" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW76" s="3"/>
+      <c r="BX76" s="3"/>
+      <c r="BY76" s="3"/>
+    </row>
+    <row r="77" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -6944,8 +7330,11 @@
       <c r="BT77" s="3"/>
       <c r="BU77" s="3"/>
       <c r="BV77" s="3"/>
-    </row>
-    <row r="78" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW77" s="3"/>
+      <c r="BX77" s="3"/>
+      <c r="BY77" s="3"/>
+    </row>
+    <row r="78" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -7018,8 +7407,11 @@
       <c r="BT78" s="3"/>
       <c r="BU78" s="3"/>
       <c r="BV78" s="3"/>
-    </row>
-    <row r="79" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW78" s="3"/>
+      <c r="BX78" s="3"/>
+      <c r="BY78" s="3"/>
+    </row>
+    <row r="79" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -7092,8 +7484,11 @@
       <c r="BT79" s="3"/>
       <c r="BU79" s="3"/>
       <c r="BV79" s="3"/>
-    </row>
-    <row r="80" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW79" s="3"/>
+      <c r="BX79" s="3"/>
+      <c r="BY79" s="3"/>
+    </row>
+    <row r="80" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -7166,8 +7561,11 @@
       <c r="BT80" s="3"/>
       <c r="BU80" s="3"/>
       <c r="BV80" s="3"/>
-    </row>
-    <row r="81" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW80" s="3"/>
+      <c r="BX80" s="3"/>
+      <c r="BY80" s="3"/>
+    </row>
+    <row r="81" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -7240,8 +7638,11 @@
       <c r="BT81" s="3"/>
       <c r="BU81" s="3"/>
       <c r="BV81" s="3"/>
-    </row>
-    <row r="82" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW81" s="3"/>
+      <c r="BX81" s="3"/>
+      <c r="BY81" s="3"/>
+    </row>
+    <row r="82" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -7314,8 +7715,11 @@
       <c r="BT82" s="3"/>
       <c r="BU82" s="3"/>
       <c r="BV82" s="3"/>
-    </row>
-    <row r="83" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW82" s="3"/>
+      <c r="BX82" s="3"/>
+      <c r="BY82" s="3"/>
+    </row>
+    <row r="83" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -7388,8 +7792,11 @@
       <c r="BT83" s="3"/>
       <c r="BU83" s="3"/>
       <c r="BV83" s="3"/>
-    </row>
-    <row r="84" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW83" s="3"/>
+      <c r="BX83" s="3"/>
+      <c r="BY83" s="3"/>
+    </row>
+    <row r="84" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -7462,8 +7869,11 @@
       <c r="BT84" s="3"/>
       <c r="BU84" s="3"/>
       <c r="BV84" s="3"/>
-    </row>
-    <row r="85" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW84" s="3"/>
+      <c r="BX84" s="3"/>
+      <c r="BY84" s="3"/>
+    </row>
+    <row r="85" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -7536,8 +7946,11 @@
       <c r="BT85" s="3"/>
       <c r="BU85" s="3"/>
       <c r="BV85" s="3"/>
-    </row>
-    <row r="86" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW85" s="3"/>
+      <c r="BX85" s="3"/>
+      <c r="BY85" s="3"/>
+    </row>
+    <row r="86" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -7610,8 +8023,11 @@
       <c r="BT86" s="3"/>
       <c r="BU86" s="3"/>
       <c r="BV86" s="3"/>
-    </row>
-    <row r="87" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW86" s="3"/>
+      <c r="BX86" s="3"/>
+      <c r="BY86" s="3"/>
+    </row>
+    <row r="87" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -7684,8 +8100,11 @@
       <c r="BT87" s="3"/>
       <c r="BU87" s="3"/>
       <c r="BV87" s="3"/>
-    </row>
-    <row r="88" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW87" s="3"/>
+      <c r="BX87" s="3"/>
+      <c r="BY87" s="3"/>
+    </row>
+    <row r="88" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -7758,8 +8177,11 @@
       <c r="BT88" s="3"/>
       <c r="BU88" s="3"/>
       <c r="BV88" s="3"/>
-    </row>
-    <row r="89" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW88" s="3"/>
+      <c r="BX88" s="3"/>
+      <c r="BY88" s="3"/>
+    </row>
+    <row r="89" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -7832,8 +8254,11 @@
       <c r="BT89" s="3"/>
       <c r="BU89" s="3"/>
       <c r="BV89" s="3"/>
-    </row>
-    <row r="90" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW89" s="3"/>
+      <c r="BX89" s="3"/>
+      <c r="BY89" s="3"/>
+    </row>
+    <row r="90" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -7906,8 +8331,11 @@
       <c r="BT90" s="3"/>
       <c r="BU90" s="3"/>
       <c r="BV90" s="3"/>
-    </row>
-    <row r="91" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW90" s="3"/>
+      <c r="BX90" s="3"/>
+      <c r="BY90" s="3"/>
+    </row>
+    <row r="91" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -7980,8 +8408,11 @@
       <c r="BT91" s="3"/>
       <c r="BU91" s="3"/>
       <c r="BV91" s="3"/>
-    </row>
-    <row r="92" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW91" s="3"/>
+      <c r="BX91" s="3"/>
+      <c r="BY91" s="3"/>
+    </row>
+    <row r="92" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -8054,8 +8485,11 @@
       <c r="BT92" s="3"/>
       <c r="BU92" s="3"/>
       <c r="BV92" s="3"/>
-    </row>
-    <row r="93" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW92" s="3"/>
+      <c r="BX92" s="3"/>
+      <c r="BY92" s="3"/>
+    </row>
+    <row r="93" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -8128,8 +8562,11 @@
       <c r="BT93" s="3"/>
       <c r="BU93" s="3"/>
       <c r="BV93" s="3"/>
-    </row>
-    <row r="94" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW93" s="3"/>
+      <c r="BX93" s="3"/>
+      <c r="BY93" s="3"/>
+    </row>
+    <row r="94" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -8202,8 +8639,11 @@
       <c r="BT94" s="3"/>
       <c r="BU94" s="3"/>
       <c r="BV94" s="3"/>
-    </row>
-    <row r="95" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW94" s="3"/>
+      <c r="BX94" s="3"/>
+      <c r="BY94" s="3"/>
+    </row>
+    <row r="95" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -8276,8 +8716,11 @@
       <c r="BT95" s="3"/>
       <c r="BU95" s="3"/>
       <c r="BV95" s="3"/>
-    </row>
-    <row r="96" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW95" s="3"/>
+      <c r="BX95" s="3"/>
+      <c r="BY95" s="3"/>
+    </row>
+    <row r="96" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -8350,8 +8793,11 @@
       <c r="BT96" s="3"/>
       <c r="BU96" s="3"/>
       <c r="BV96" s="3"/>
-    </row>
-    <row r="97" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW96" s="3"/>
+      <c r="BX96" s="3"/>
+      <c r="BY96" s="3"/>
+    </row>
+    <row r="97" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -8424,8 +8870,11 @@
       <c r="BT97" s="3"/>
       <c r="BU97" s="3"/>
       <c r="BV97" s="3"/>
-    </row>
-    <row r="98" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW97" s="3"/>
+      <c r="BX97" s="3"/>
+      <c r="BY97" s="3"/>
+    </row>
+    <row r="98" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -8498,8 +8947,11 @@
       <c r="BT98" s="3"/>
       <c r="BU98" s="3"/>
       <c r="BV98" s="3"/>
-    </row>
-    <row r="99" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW98" s="3"/>
+      <c r="BX98" s="3"/>
+      <c r="BY98" s="3"/>
+    </row>
+    <row r="99" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -8572,8 +9024,11 @@
       <c r="BT99" s="3"/>
       <c r="BU99" s="3"/>
       <c r="BV99" s="3"/>
-    </row>
-    <row r="100" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW99" s="3"/>
+      <c r="BX99" s="3"/>
+      <c r="BY99" s="3"/>
+    </row>
+    <row r="100" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -8646,8 +9101,11 @@
       <c r="BT100" s="3"/>
       <c r="BU100" s="3"/>
       <c r="BV100" s="3"/>
-    </row>
-    <row r="101" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW100" s="3"/>
+      <c r="BX100" s="3"/>
+      <c r="BY100" s="3"/>
+    </row>
+    <row r="101" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -8720,8 +9178,11 @@
       <c r="BT101" s="3"/>
       <c r="BU101" s="3"/>
       <c r="BV101" s="3"/>
-    </row>
-    <row r="102" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW101" s="3"/>
+      <c r="BX101" s="3"/>
+      <c r="BY101" s="3"/>
+    </row>
+    <row r="102" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -8794,8 +9255,11 @@
       <c r="BT102" s="3"/>
       <c r="BU102" s="3"/>
       <c r="BV102" s="3"/>
-    </row>
-    <row r="103" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW102" s="3"/>
+      <c r="BX102" s="3"/>
+      <c r="BY102" s="3"/>
+    </row>
+    <row r="103" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -8868,8 +9332,11 @@
       <c r="BT103" s="3"/>
       <c r="BU103" s="3"/>
       <c r="BV103" s="3"/>
-    </row>
-    <row r="104" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW103" s="3"/>
+      <c r="BX103" s="3"/>
+      <c r="BY103" s="3"/>
+    </row>
+    <row r="104" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -8942,8 +9409,11 @@
       <c r="BT104" s="3"/>
       <c r="BU104" s="3"/>
       <c r="BV104" s="3"/>
-    </row>
-    <row r="105" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW104" s="3"/>
+      <c r="BX104" s="3"/>
+      <c r="BY104" s="3"/>
+    </row>
+    <row r="105" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -9016,8 +9486,11 @@
       <c r="BT105" s="3"/>
       <c r="BU105" s="3"/>
       <c r="BV105" s="3"/>
-    </row>
-    <row r="106" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW105" s="3"/>
+      <c r="BX105" s="3"/>
+      <c r="BY105" s="3"/>
+    </row>
+    <row r="106" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -9090,8 +9563,11 @@
       <c r="BT106" s="3"/>
       <c r="BU106" s="3"/>
       <c r="BV106" s="3"/>
-    </row>
-    <row r="107" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW106" s="3"/>
+      <c r="BX106" s="3"/>
+      <c r="BY106" s="3"/>
+    </row>
+    <row r="107" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -9164,8 +9640,11 @@
       <c r="BT107" s="3"/>
       <c r="BU107" s="3"/>
       <c r="BV107" s="3"/>
-    </row>
-    <row r="108" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW107" s="3"/>
+      <c r="BX107" s="3"/>
+      <c r="BY107" s="3"/>
+    </row>
+    <row r="108" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -9238,8 +9717,11 @@
       <c r="BT108" s="3"/>
       <c r="BU108" s="3"/>
       <c r="BV108" s="3"/>
-    </row>
-    <row r="109" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW108" s="3"/>
+      <c r="BX108" s="3"/>
+      <c r="BY108" s="3"/>
+    </row>
+    <row r="109" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -9312,8 +9794,11 @@
       <c r="BT109" s="3"/>
       <c r="BU109" s="3"/>
       <c r="BV109" s="3"/>
-    </row>
-    <row r="110" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW109" s="3"/>
+      <c r="BX109" s="3"/>
+      <c r="BY109" s="3"/>
+    </row>
+    <row r="110" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -9386,8 +9871,11 @@
       <c r="BT110" s="3"/>
       <c r="BU110" s="3"/>
       <c r="BV110" s="3"/>
-    </row>
-    <row r="111" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW110" s="3"/>
+      <c r="BX110" s="3"/>
+      <c r="BY110" s="3"/>
+    </row>
+    <row r="111" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -9460,8 +9948,11 @@
       <c r="BT111" s="3"/>
       <c r="BU111" s="3"/>
       <c r="BV111" s="3"/>
-    </row>
-    <row r="112" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW111" s="3"/>
+      <c r="BX111" s="3"/>
+      <c r="BY111" s="3"/>
+    </row>
+    <row r="112" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -9534,8 +10025,11 @@
       <c r="BT112" s="3"/>
       <c r="BU112" s="3"/>
       <c r="BV112" s="3"/>
-    </row>
-    <row r="113" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW112" s="3"/>
+      <c r="BX112" s="3"/>
+      <c r="BY112" s="3"/>
+    </row>
+    <row r="113" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -9608,8 +10102,11 @@
       <c r="BT113" s="3"/>
       <c r="BU113" s="3"/>
       <c r="BV113" s="3"/>
-    </row>
-    <row r="114" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW113" s="3"/>
+      <c r="BX113" s="3"/>
+      <c r="BY113" s="3"/>
+    </row>
+    <row r="114" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -9682,8 +10179,11 @@
       <c r="BT114" s="3"/>
       <c r="BU114" s="3"/>
       <c r="BV114" s="3"/>
-    </row>
-    <row r="115" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW114" s="3"/>
+      <c r="BX114" s="3"/>
+      <c r="BY114" s="3"/>
+    </row>
+    <row r="115" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -9756,8 +10256,11 @@
       <c r="BT115" s="3"/>
       <c r="BU115" s="3"/>
       <c r="BV115" s="3"/>
-    </row>
-    <row r="116" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW115" s="3"/>
+      <c r="BX115" s="3"/>
+      <c r="BY115" s="3"/>
+    </row>
+    <row r="116" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -9830,8 +10333,11 @@
       <c r="BT116" s="3"/>
       <c r="BU116" s="3"/>
       <c r="BV116" s="3"/>
-    </row>
-    <row r="117" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW116" s="3"/>
+      <c r="BX116" s="3"/>
+      <c r="BY116" s="3"/>
+    </row>
+    <row r="117" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -9904,8 +10410,11 @@
       <c r="BT117" s="3"/>
       <c r="BU117" s="3"/>
       <c r="BV117" s="3"/>
-    </row>
-    <row r="118" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW117" s="3"/>
+      <c r="BX117" s="3"/>
+      <c r="BY117" s="3"/>
+    </row>
+    <row r="118" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -9978,8 +10487,11 @@
       <c r="BT118" s="3"/>
       <c r="BU118" s="3"/>
       <c r="BV118" s="3"/>
-    </row>
-    <row r="119" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW118" s="3"/>
+      <c r="BX118" s="3"/>
+      <c r="BY118" s="3"/>
+    </row>
+    <row r="119" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -10052,8 +10564,11 @@
       <c r="BT119" s="3"/>
       <c r="BU119" s="3"/>
       <c r="BV119" s="3"/>
-    </row>
-    <row r="120" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW119" s="3"/>
+      <c r="BX119" s="3"/>
+      <c r="BY119" s="3"/>
+    </row>
+    <row r="120" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -10126,8 +10641,11 @@
       <c r="BT120" s="3"/>
       <c r="BU120" s="3"/>
       <c r="BV120" s="3"/>
-    </row>
-    <row r="121" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW120" s="3"/>
+      <c r="BX120" s="3"/>
+      <c r="BY120" s="3"/>
+    </row>
+    <row r="121" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -10200,8 +10718,11 @@
       <c r="BT121" s="3"/>
       <c r="BU121" s="3"/>
       <c r="BV121" s="3"/>
-    </row>
-    <row r="122" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW121" s="3"/>
+      <c r="BX121" s="3"/>
+      <c r="BY121" s="3"/>
+    </row>
+    <row r="122" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -10274,8 +10795,11 @@
       <c r="BT122" s="3"/>
       <c r="BU122" s="3"/>
       <c r="BV122" s="3"/>
-    </row>
-    <row r="123" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW122" s="3"/>
+      <c r="BX122" s="3"/>
+      <c r="BY122" s="3"/>
+    </row>
+    <row r="123" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -10348,8 +10872,11 @@
       <c r="BT123" s="3"/>
       <c r="BU123" s="3"/>
       <c r="BV123" s="3"/>
-    </row>
-    <row r="124" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW123" s="3"/>
+      <c r="BX123" s="3"/>
+      <c r="BY123" s="3"/>
+    </row>
+    <row r="124" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -10422,8 +10949,11 @@
       <c r="BT124" s="3"/>
       <c r="BU124" s="3"/>
       <c r="BV124" s="3"/>
-    </row>
-    <row r="125" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW124" s="3"/>
+      <c r="BX124" s="3"/>
+      <c r="BY124" s="3"/>
+    </row>
+    <row r="125" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -10496,8 +11026,11 @@
       <c r="BT125" s="3"/>
       <c r="BU125" s="3"/>
       <c r="BV125" s="3"/>
-    </row>
-    <row r="126" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW125" s="3"/>
+      <c r="BX125" s="3"/>
+      <c r="BY125" s="3"/>
+    </row>
+    <row r="126" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -10570,8 +11103,11 @@
       <c r="BT126" s="3"/>
       <c r="BU126" s="3"/>
       <c r="BV126" s="3"/>
-    </row>
-    <row r="127" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW126" s="3"/>
+      <c r="BX126" s="3"/>
+      <c r="BY126" s="3"/>
+    </row>
+    <row r="127" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -10644,8 +11180,11 @@
       <c r="BT127" s="3"/>
       <c r="BU127" s="3"/>
       <c r="BV127" s="3"/>
-    </row>
-    <row r="128" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW127" s="3"/>
+      <c r="BX127" s="3"/>
+      <c r="BY127" s="3"/>
+    </row>
+    <row r="128" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -10718,8 +11257,11 @@
       <c r="BT128" s="3"/>
       <c r="BU128" s="3"/>
       <c r="BV128" s="3"/>
-    </row>
-    <row r="129" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW128" s="3"/>
+      <c r="BX128" s="3"/>
+      <c r="BY128" s="3"/>
+    </row>
+    <row r="129" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -10792,8 +11334,11 @@
       <c r="BT129" s="3"/>
       <c r="BU129" s="3"/>
       <c r="BV129" s="3"/>
-    </row>
-    <row r="130" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW129" s="3"/>
+      <c r="BX129" s="3"/>
+      <c r="BY129" s="3"/>
+    </row>
+    <row r="130" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -10866,8 +11411,11 @@
       <c r="BT130" s="3"/>
       <c r="BU130" s="3"/>
       <c r="BV130" s="3"/>
-    </row>
-    <row r="131" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW130" s="3"/>
+      <c r="BX130" s="3"/>
+      <c r="BY130" s="3"/>
+    </row>
+    <row r="131" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -10940,8 +11488,11 @@
       <c r="BT131" s="3"/>
       <c r="BU131" s="3"/>
       <c r="BV131" s="3"/>
-    </row>
-    <row r="132" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW131" s="3"/>
+      <c r="BX131" s="3"/>
+      <c r="BY131" s="3"/>
+    </row>
+    <row r="132" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -11014,8 +11565,11 @@
       <c r="BT132" s="3"/>
       <c r="BU132" s="3"/>
       <c r="BV132" s="3"/>
-    </row>
-    <row r="133" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW132" s="3"/>
+      <c r="BX132" s="3"/>
+      <c r="BY132" s="3"/>
+    </row>
+    <row r="133" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -11088,8 +11642,11 @@
       <c r="BT133" s="3"/>
       <c r="BU133" s="3"/>
       <c r="BV133" s="3"/>
-    </row>
-    <row r="134" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW133" s="3"/>
+      <c r="BX133" s="3"/>
+      <c r="BY133" s="3"/>
+    </row>
+    <row r="134" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -11162,8 +11719,11 @@
       <c r="BT134" s="3"/>
       <c r="BU134" s="3"/>
       <c r="BV134" s="3"/>
-    </row>
-    <row r="135" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW134" s="3"/>
+      <c r="BX134" s="3"/>
+      <c r="BY134" s="3"/>
+    </row>
+    <row r="135" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -11236,8 +11796,11 @@
       <c r="BT135" s="3"/>
       <c r="BU135" s="3"/>
       <c r="BV135" s="3"/>
-    </row>
-    <row r="136" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW135" s="3"/>
+      <c r="BX135" s="3"/>
+      <c r="BY135" s="3"/>
+    </row>
+    <row r="136" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -11310,8 +11873,11 @@
       <c r="BT136" s="3"/>
       <c r="BU136" s="3"/>
       <c r="BV136" s="3"/>
-    </row>
-    <row r="137" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW136" s="3"/>
+      <c r="BX136" s="3"/>
+      <c r="BY136" s="3"/>
+    </row>
+    <row r="137" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -11384,8 +11950,11 @@
       <c r="BT137" s="3"/>
       <c r="BU137" s="3"/>
       <c r="BV137" s="3"/>
-    </row>
-    <row r="138" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW137" s="3"/>
+      <c r="BX137" s="3"/>
+      <c r="BY137" s="3"/>
+    </row>
+    <row r="138" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -11458,8 +12027,11 @@
       <c r="BT138" s="3"/>
       <c r="BU138" s="3"/>
       <c r="BV138" s="3"/>
-    </row>
-    <row r="139" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW138" s="3"/>
+      <c r="BX138" s="3"/>
+      <c r="BY138" s="3"/>
+    </row>
+    <row r="139" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -11532,8 +12104,11 @@
       <c r="BT139" s="3"/>
       <c r="BU139" s="3"/>
       <c r="BV139" s="3"/>
-    </row>
-    <row r="140" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW139" s="3"/>
+      <c r="BX139" s="3"/>
+      <c r="BY139" s="3"/>
+    </row>
+    <row r="140" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -11606,8 +12181,11 @@
       <c r="BT140" s="3"/>
       <c r="BU140" s="3"/>
       <c r="BV140" s="3"/>
-    </row>
-    <row r="141" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW140" s="3"/>
+      <c r="BX140" s="3"/>
+      <c r="BY140" s="3"/>
+    </row>
+    <row r="141" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -11680,8 +12258,11 @@
       <c r="BT141" s="3"/>
       <c r="BU141" s="3"/>
       <c r="BV141" s="3"/>
-    </row>
-    <row r="142" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW141" s="3"/>
+      <c r="BX141" s="3"/>
+      <c r="BY141" s="3"/>
+    </row>
+    <row r="142" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -11754,8 +12335,11 @@
       <c r="BT142" s="3"/>
       <c r="BU142" s="3"/>
       <c r="BV142" s="3"/>
-    </row>
-    <row r="143" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW142" s="3"/>
+      <c r="BX142" s="3"/>
+      <c r="BY142" s="3"/>
+    </row>
+    <row r="143" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -11828,8 +12412,11 @@
       <c r="BT143" s="3"/>
       <c r="BU143" s="3"/>
       <c r="BV143" s="3"/>
-    </row>
-    <row r="144" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW143" s="3"/>
+      <c r="BX143" s="3"/>
+      <c r="BY143" s="3"/>
+    </row>
+    <row r="144" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -11902,8 +12489,11 @@
       <c r="BT144" s="3"/>
       <c r="BU144" s="3"/>
       <c r="BV144" s="3"/>
-    </row>
-    <row r="145" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW144" s="3"/>
+      <c r="BX144" s="3"/>
+      <c r="BY144" s="3"/>
+    </row>
+    <row r="145" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -11976,8 +12566,11 @@
       <c r="BT145" s="3"/>
       <c r="BU145" s="3"/>
       <c r="BV145" s="3"/>
-    </row>
-    <row r="146" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW145" s="3"/>
+      <c r="BX145" s="3"/>
+      <c r="BY145" s="3"/>
+    </row>
+    <row r="146" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -12050,8 +12643,11 @@
       <c r="BT146" s="3"/>
       <c r="BU146" s="3"/>
       <c r="BV146" s="3"/>
-    </row>
-    <row r="147" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW146" s="3"/>
+      <c r="BX146" s="3"/>
+      <c r="BY146" s="3"/>
+    </row>
+    <row r="147" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -12124,8 +12720,11 @@
       <c r="BT147" s="3"/>
       <c r="BU147" s="3"/>
       <c r="BV147" s="3"/>
-    </row>
-    <row r="148" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW147" s="3"/>
+      <c r="BX147" s="3"/>
+      <c r="BY147" s="3"/>
+    </row>
+    <row r="148" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -12198,8 +12797,11 @@
       <c r="BT148" s="3"/>
       <c r="BU148" s="3"/>
       <c r="BV148" s="3"/>
-    </row>
-    <row r="149" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW148" s="3"/>
+      <c r="BX148" s="3"/>
+      <c r="BY148" s="3"/>
+    </row>
+    <row r="149" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -12272,8 +12874,11 @@
       <c r="BT149" s="3"/>
       <c r="BU149" s="3"/>
       <c r="BV149" s="3"/>
-    </row>
-    <row r="150" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW149" s="3"/>
+      <c r="BX149" s="3"/>
+      <c r="BY149" s="3"/>
+    </row>
+    <row r="150" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -12346,8 +12951,11 @@
       <c r="BT150" s="3"/>
       <c r="BU150" s="3"/>
       <c r="BV150" s="3"/>
-    </row>
-    <row r="151" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW150" s="3"/>
+      <c r="BX150" s="3"/>
+      <c r="BY150" s="3"/>
+    </row>
+    <row r="151" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -12420,8 +13028,11 @@
       <c r="BT151" s="3"/>
       <c r="BU151" s="3"/>
       <c r="BV151" s="3"/>
-    </row>
-    <row r="152" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW151" s="3"/>
+      <c r="BX151" s="3"/>
+      <c r="BY151" s="3"/>
+    </row>
+    <row r="152" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -12494,8 +13105,11 @@
       <c r="BT152" s="3"/>
       <c r="BU152" s="3"/>
       <c r="BV152" s="3"/>
-    </row>
-    <row r="153" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW152" s="3"/>
+      <c r="BX152" s="3"/>
+      <c r="BY152" s="3"/>
+    </row>
+    <row r="153" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -12568,8 +13182,11 @@
       <c r="BT153" s="3"/>
       <c r="BU153" s="3"/>
       <c r="BV153" s="3"/>
-    </row>
-    <row r="154" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW153" s="3"/>
+      <c r="BX153" s="3"/>
+      <c r="BY153" s="3"/>
+    </row>
+    <row r="154" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -12642,8 +13259,11 @@
       <c r="BT154" s="3"/>
       <c r="BU154" s="3"/>
       <c r="BV154" s="3"/>
-    </row>
-    <row r="155" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW154" s="3"/>
+      <c r="BX154" s="3"/>
+      <c r="BY154" s="3"/>
+    </row>
+    <row r="155" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -12716,8 +13336,11 @@
       <c r="BT155" s="3"/>
       <c r="BU155" s="3"/>
       <c r="BV155" s="3"/>
-    </row>
-    <row r="156" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW155" s="3"/>
+      <c r="BX155" s="3"/>
+      <c r="BY155" s="3"/>
+    </row>
+    <row r="156" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -12790,8 +13413,11 @@
       <c r="BT156" s="3"/>
       <c r="BU156" s="3"/>
       <c r="BV156" s="3"/>
-    </row>
-    <row r="157" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW156" s="3"/>
+      <c r="BX156" s="3"/>
+      <c r="BY156" s="3"/>
+    </row>
+    <row r="157" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -12864,8 +13490,11 @@
       <c r="BT157" s="3"/>
       <c r="BU157" s="3"/>
       <c r="BV157" s="3"/>
-    </row>
-    <row r="158" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW157" s="3"/>
+      <c r="BX157" s="3"/>
+      <c r="BY157" s="3"/>
+    </row>
+    <row r="158" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -12938,8 +13567,11 @@
       <c r="BT158" s="3"/>
       <c r="BU158" s="3"/>
       <c r="BV158" s="3"/>
-    </row>
-    <row r="159" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW158" s="3"/>
+      <c r="BX158" s="3"/>
+      <c r="BY158" s="3"/>
+    </row>
+    <row r="159" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -13012,8 +13644,11 @@
       <c r="BT159" s="3"/>
       <c r="BU159" s="3"/>
       <c r="BV159" s="3"/>
-    </row>
-    <row r="160" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW159" s="3"/>
+      <c r="BX159" s="3"/>
+      <c r="BY159" s="3"/>
+    </row>
+    <row r="160" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -13086,8 +13721,11 @@
       <c r="BT160" s="3"/>
       <c r="BU160" s="3"/>
       <c r="BV160" s="3"/>
-    </row>
-    <row r="161" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW160" s="3"/>
+      <c r="BX160" s="3"/>
+      <c r="BY160" s="3"/>
+    </row>
+    <row r="161" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -13160,8 +13798,11 @@
       <c r="BT161" s="3"/>
       <c r="BU161" s="3"/>
       <c r="BV161" s="3"/>
-    </row>
-    <row r="162" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW161" s="3"/>
+      <c r="BX161" s="3"/>
+      <c r="BY161" s="3"/>
+    </row>
+    <row r="162" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -13234,8 +13875,11 @@
       <c r="BT162" s="3"/>
       <c r="BU162" s="3"/>
       <c r="BV162" s="3"/>
-    </row>
-    <row r="163" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW162" s="3"/>
+      <c r="BX162" s="3"/>
+      <c r="BY162" s="3"/>
+    </row>
+    <row r="163" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -13308,8 +13952,11 @@
       <c r="BT163" s="3"/>
       <c r="BU163" s="3"/>
       <c r="BV163" s="3"/>
-    </row>
-    <row r="164" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW163" s="3"/>
+      <c r="BX163" s="3"/>
+      <c r="BY163" s="3"/>
+    </row>
+    <row r="164" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -13382,8 +14029,11 @@
       <c r="BT164" s="3"/>
       <c r="BU164" s="3"/>
       <c r="BV164" s="3"/>
-    </row>
-    <row r="165" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW164" s="3"/>
+      <c r="BX164" s="3"/>
+      <c r="BY164" s="3"/>
+    </row>
+    <row r="165" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -13456,8 +14106,11 @@
       <c r="BT165" s="3"/>
       <c r="BU165" s="3"/>
       <c r="BV165" s="3"/>
-    </row>
-    <row r="166" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW165" s="3"/>
+      <c r="BX165" s="3"/>
+      <c r="BY165" s="3"/>
+    </row>
+    <row r="166" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -13530,8 +14183,11 @@
       <c r="BT166" s="3"/>
       <c r="BU166" s="3"/>
       <c r="BV166" s="3"/>
-    </row>
-    <row r="167" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW166" s="3"/>
+      <c r="BX166" s="3"/>
+      <c r="BY166" s="3"/>
+    </row>
+    <row r="167" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -13604,8 +14260,11 @@
       <c r="BT167" s="3"/>
       <c r="BU167" s="3"/>
       <c r="BV167" s="3"/>
-    </row>
-    <row r="168" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW167" s="3"/>
+      <c r="BX167" s="3"/>
+      <c r="BY167" s="3"/>
+    </row>
+    <row r="168" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -13678,8 +14337,11 @@
       <c r="BT168" s="3"/>
       <c r="BU168" s="3"/>
       <c r="BV168" s="3"/>
-    </row>
-    <row r="169" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW168" s="3"/>
+      <c r="BX168" s="3"/>
+      <c r="BY168" s="3"/>
+    </row>
+    <row r="169" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -13752,8 +14414,11 @@
       <c r="BT169" s="3"/>
       <c r="BU169" s="3"/>
       <c r="BV169" s="3"/>
-    </row>
-    <row r="170" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW169" s="3"/>
+      <c r="BX169" s="3"/>
+      <c r="BY169" s="3"/>
+    </row>
+    <row r="170" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -13826,8 +14491,11 @@
       <c r="BT170" s="3"/>
       <c r="BU170" s="3"/>
       <c r="BV170" s="3"/>
-    </row>
-    <row r="171" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW170" s="3"/>
+      <c r="BX170" s="3"/>
+      <c r="BY170" s="3"/>
+    </row>
+    <row r="171" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -13900,8 +14568,11 @@
       <c r="BT171" s="3"/>
       <c r="BU171" s="3"/>
       <c r="BV171" s="3"/>
-    </row>
-    <row r="172" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW171" s="3"/>
+      <c r="BX171" s="3"/>
+      <c r="BY171" s="3"/>
+    </row>
+    <row r="172" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -13974,8 +14645,11 @@
       <c r="BT172" s="3"/>
       <c r="BU172" s="3"/>
       <c r="BV172" s="3"/>
-    </row>
-    <row r="173" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW172" s="3"/>
+      <c r="BX172" s="3"/>
+      <c r="BY172" s="3"/>
+    </row>
+    <row r="173" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -14048,8 +14722,11 @@
       <c r="BT173" s="3"/>
       <c r="BU173" s="3"/>
       <c r="BV173" s="3"/>
-    </row>
-    <row r="174" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW173" s="3"/>
+      <c r="BX173" s="3"/>
+      <c r="BY173" s="3"/>
+    </row>
+    <row r="174" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -14122,8 +14799,11 @@
       <c r="BT174" s="3"/>
       <c r="BU174" s="3"/>
       <c r="BV174" s="3"/>
-    </row>
-    <row r="175" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW174" s="3"/>
+      <c r="BX174" s="3"/>
+      <c r="BY174" s="3"/>
+    </row>
+    <row r="175" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -14196,8 +14876,11 @@
       <c r="BT175" s="3"/>
       <c r="BU175" s="3"/>
       <c r="BV175" s="3"/>
-    </row>
-    <row r="176" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW175" s="3"/>
+      <c r="BX175" s="3"/>
+      <c r="BY175" s="3"/>
+    </row>
+    <row r="176" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -14270,8 +14953,11 @@
       <c r="BT176" s="3"/>
       <c r="BU176" s="3"/>
       <c r="BV176" s="3"/>
-    </row>
-    <row r="177" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW176" s="3"/>
+      <c r="BX176" s="3"/>
+      <c r="BY176" s="3"/>
+    </row>
+    <row r="177" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -14344,8 +15030,11 @@
       <c r="BT177" s="3"/>
       <c r="BU177" s="3"/>
       <c r="BV177" s="3"/>
-    </row>
-    <row r="178" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW177" s="3"/>
+      <c r="BX177" s="3"/>
+      <c r="BY177" s="3"/>
+    </row>
+    <row r="178" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -14418,8 +15107,11 @@
       <c r="BT178" s="3"/>
       <c r="BU178" s="3"/>
       <c r="BV178" s="3"/>
-    </row>
-    <row r="179" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW178" s="3"/>
+      <c r="BX178" s="3"/>
+      <c r="BY178" s="3"/>
+    </row>
+    <row r="179" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -14492,8 +15184,11 @@
       <c r="BT179" s="3"/>
       <c r="BU179" s="3"/>
       <c r="BV179" s="3"/>
-    </row>
-    <row r="180" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW179" s="3"/>
+      <c r="BX179" s="3"/>
+      <c r="BY179" s="3"/>
+    </row>
+    <row r="180" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -14566,8 +15261,11 @@
       <c r="BT180" s="3"/>
       <c r="BU180" s="3"/>
       <c r="BV180" s="3"/>
-    </row>
-    <row r="181" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW180" s="3"/>
+      <c r="BX180" s="3"/>
+      <c r="BY180" s="3"/>
+    </row>
+    <row r="181" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -14640,8 +15338,11 @@
       <c r="BT181" s="3"/>
       <c r="BU181" s="3"/>
       <c r="BV181" s="3"/>
-    </row>
-    <row r="182" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW181" s="3"/>
+      <c r="BX181" s="3"/>
+      <c r="BY181" s="3"/>
+    </row>
+    <row r="182" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -14714,8 +15415,11 @@
       <c r="BT182" s="3"/>
       <c r="BU182" s="3"/>
       <c r="BV182" s="3"/>
-    </row>
-    <row r="183" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW182" s="3"/>
+      <c r="BX182" s="3"/>
+      <c r="BY182" s="3"/>
+    </row>
+    <row r="183" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -14788,8 +15492,11 @@
       <c r="BT183" s="3"/>
       <c r="BU183" s="3"/>
       <c r="BV183" s="3"/>
-    </row>
-    <row r="184" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW183" s="3"/>
+      <c r="BX183" s="3"/>
+      <c r="BY183" s="3"/>
+    </row>
+    <row r="184" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -14862,8 +15569,11 @@
       <c r="BT184" s="3"/>
       <c r="BU184" s="3"/>
       <c r="BV184" s="3"/>
-    </row>
-    <row r="185" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW184" s="3"/>
+      <c r="BX184" s="3"/>
+      <c r="BY184" s="3"/>
+    </row>
+    <row r="185" spans="3:77" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -14936,11 +15646,15 @@
       <c r="BT185" s="3"/>
       <c r="BU185" s="3"/>
       <c r="BV185" s="3"/>
+      <c r="BW185" s="3"/>
+      <c r="BX185" s="3"/>
+      <c r="BY185" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{A8C76D48-F522-4C09-BD43-42B6B98FB181}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>